--- a/backend/data/financials_by_company/1F1.SI.xlsx
+++ b/backend/data/financials_by_company/1F1.SI.xlsx
@@ -3875,10 +3875,8 @@
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>038987</t>
-        </is>
+      <c r="D2" t="n">
+        <v>38987</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4090,7 +4088,7 @@
         <v>-545478</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
         <v>0.157</v>
@@ -4322,7 +4320,7 @@
         <v>0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA2" t="n">
         <v>-0.00057999976</v>
